--- a/reports/China_Town_Assets_Details_2026.xlsx
+++ b/reports/China_Town_Assets_Details_2026.xlsx
@@ -12,7 +12,16 @@
     <sheet name="CT Baby Room" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CT Assets Summery" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'CT Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CT Washroom Details'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'CT Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'CT Handicap Washroom'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'CT Baby Room'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'CT Baby Room'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'CT Assets Summery'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'CT Assets Summery'!$A$1:$H$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -547,7 +556,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -908,6 +917,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -915,7 +925,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1177,6 +1187,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1184,7 +1195,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1401,6 +1412,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1408,7 +1420,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1513,5 +1525,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/reports/China_Town_Assets_Details_2026.xlsx
+++ b/reports/China_Town_Assets_Details_2026.xlsx
@@ -1398,8 +1398,8 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
